--- a/测试集/边缘情况/表头不在第一行.xlsx
+++ b/测试集/边缘情况/表头不在第一行.xlsx
@@ -495,23 +495,23 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46208</v>
+        <v>46248</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>北京中科联合实业有限公司</t>
+          <t>武汉江城建材经营部</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HT-4486</t>
+          <t>HT-6332</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>104190.77</v>
+        <v>167177.41</v>
       </c>
       <c r="E3" t="n">
-        <v>86891.64</v>
+        <v>141116.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,127 +521,127 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46220</v>
+        <v>46253</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南京新视野广告工作室</t>
+          <t>成都锦绣家园物业管理有限公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HT-5099</t>
+          <t>HT-9023</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>135677.17</v>
+        <v>107507.97</v>
       </c>
       <c r="E4" t="n">
-        <v>125809.8</v>
+        <v>106328.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>逾期</t>
+          <t>已到账</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46243</v>
+        <v>46252</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>杭州明启科技有限公司</t>
+          <t>成都锦绣家园物业管理有限公司</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HT-8576</t>
+          <t>HT-9100</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16538.97</v>
+        <v>114046.64</v>
       </c>
       <c r="E5" t="n">
-        <v>15204.69</v>
+        <v>108186.75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>部分到账</t>
+          <t>已到账</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46256</v>
+        <v>46231</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>北京中科联合实业有限公司</t>
+          <t>深圳市恒信电子有限公司</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HT-7688</t>
+          <t>HT-6044</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>114545.3</v>
+        <v>25863.15</v>
       </c>
       <c r="E6" t="n">
-        <v>106056.06</v>
+        <v>23886.03</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>逾期</t>
+          <t>部分到账</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46269</v>
+        <v>46224</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>广州云图文化传媒有限公司</t>
+          <t>武汉江城建材经营部</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HT-8588</t>
+          <t>HT-6228</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>176955.24</v>
+        <v>199512.67</v>
       </c>
       <c r="E7" t="n">
-        <v>165093.28</v>
+        <v>167172.08</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>逾期</t>
+          <t>已到账</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46248</v>
+        <v>46216</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>武汉江城建材经营部</t>
+          <t>上海岚图贸易有限公司</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HT-6332</t>
+          <t>HT-3806</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>103675.07</v>
+        <v>111342.8</v>
       </c>
       <c r="E8" t="n">
-        <v>87513.21000000001</v>
+        <v>97926.98</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -651,49 +651,49 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46253</v>
+        <v>46285</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>成都锦绣家园物业管理有限公司</t>
+          <t>上海岚图贸易有限公司</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HT-9023</t>
+          <t>HT-5436</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>107507.97</v>
+        <v>122290.33</v>
       </c>
       <c r="E9" t="n">
-        <v>106328.98</v>
+        <v>103580.06</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>已到账</t>
+          <t>部分到账</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46252</v>
+        <v>46216</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>成都锦绣家园物业管理有限公司</t>
+          <t>上海岚图贸易有限公司</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HT-9100</t>
+          <t>HT-8266</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>114046.64</v>
+        <v>180008.72</v>
       </c>
       <c r="E10" t="n">
-        <v>108186.75</v>
+        <v>156310.73</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -703,49 +703,49 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46231</v>
+        <v>46256</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>深圳市恒信电子有限公司</t>
+          <t>上海岚图贸易有限公司</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HT-6044</t>
+          <t>HT-7298</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25863.15</v>
+        <v>94881.16</v>
       </c>
       <c r="E11" t="n">
-        <v>23886.03</v>
+        <v>77906.53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>部分到账</t>
+          <t>已到账</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46224</v>
+        <v>46274</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>武汉江城建材经营部</t>
+          <t>南京新视野广告工作室</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HT-6228</t>
+          <t>HT-4818</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>199512.67</v>
+        <v>175464.81</v>
       </c>
       <c r="E12" t="n">
-        <v>167172.08</v>
+        <v>161232.71</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
